--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R3" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R4" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>90745</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R3" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>90744</v>
+        <v>98140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R4" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90745</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98140</v>
+        <v>90754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
+        <v>90761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R3" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>90754</v>
+        <v>98157</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R4" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90763</v>
+        <v>98159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98159</v>
+        <v>90763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 23115-2024 artfynd.xlsx
+++ b/artfynd/A 23115-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121747235</v>
+        <v>121792902</v>
       </c>
       <c r="B2" t="n">
-        <v>98157</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533207</v>
+        <v>533320</v>
       </c>
       <c r="R2" t="n">
-        <v>6332391</v>
+        <v>6332395</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,53 +772,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121793765</v>
+        <v>67498490</v>
       </c>
       <c r="B3" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5741</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grönelund, Grönelund, Sm</t>
+          <t>Mösjöhult (1 km söder om), Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533234</v>
+        <v>533151</v>
       </c>
       <c r="R3" t="n">
-        <v>6332386</v>
+        <v>6332373</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +840,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2017-09-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2017-09-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>stor gul ramaria troligen flavescens</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,55 +869,56 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog med inslag av kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tobias Ivarsson, Johan Marand, Per Darell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792902</v>
+        <v>121747235</v>
       </c>
       <c r="B4" t="n">
-        <v>90763</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533320</v>
+        <v>533207</v>
       </c>
       <c r="R4" t="n">
-        <v>6332395</v>
+        <v>6332391</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,6 +987,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121793765</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grönelund, Grönelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533234</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6332386</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
